--- a/Configs/GameConfig/Datas/fg/#EnemyEncounter-敌人编成.xlsx
+++ b/Configs/GameConfig/Datas/fg/#EnemyEncounter-敌人编成.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1217,6 +1217,906 @@
         <v>110</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>rh_listen_node</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>relay_hall</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>rh_guard_w</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>enemy_listen_node</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>rh_prism</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>relay_hall</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>rh_guard_e</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>enemy_prism</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>rh_hunter_1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>relay_hall</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>rh_ambush_w</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>enemy_echo_hunter</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>rh_ambush_w</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>rh_hunter_2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>relay_hall</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>rh_ambush_e</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>enemy_echo_hunter</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>rh_ambush_e</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>rh_decoy</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>relay_hall</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>rh_decoy</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>enemy_decoy_relay</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>rh_listener</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>relay_hall</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>rh_elite</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>enemy_listener</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>rh_counter_prism</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>relay_hall</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>rh_counter_a</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>enemy_prism</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>counter_deflect</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4</v>
+      </c>
+      <c r="K24" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>rh_counter_node</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>relay_hall</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>rh_counter_a</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>enemy_listen_node</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>counter_listen</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>rh_counter_listener</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>relay_hall</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>rh_counter_b</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>enemy_listener</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>counter_listen</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>rh_counter_jammer</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>relay_hall</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>rh_counter_b</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>enemy_jammer</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>counter_jam</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>rh_node_1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>relay_hall</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>rh_node_1</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>enemy_mind_relay</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>boss</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>rh_node_2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>relay_hall</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>rh_node_2</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>enemy_mind_relay</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>boss</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>rh_node_3</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>relay_hall</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>rh_node_3</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>enemy_mind_relay</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>boss</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>rh_node_4</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>relay_hall</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>rh_node_4</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>enemy_mind_relay</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>boss</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>rh_node_5</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>relay_hall</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>rh_node_5</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>enemy_mind_relay</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>boss</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>rh_node_6</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>relay_hall</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>rh_node_6</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>enemy_mind_relay</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>boss</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>rh_mind_core</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>relay_hall</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>rh_core</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>enemy_mind_core</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>boss</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>rh_wave_hunter_1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>relay_hall</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>rh_wave_w</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>enemy_echo_hunter</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>boss_wave</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>rh_wave_w</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>rh_wave_hunter_2</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>relay_hall</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>rh_wave_e</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>enemy_echo_hunter</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>boss_wave</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>rh_wave_e</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>rh_wave_prism</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>relay_hall</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>rh_core_n</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>enemy_prism</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>boss_wave</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3</v>
+      </c>
+      <c r="K37" t="n">
+        <v>200</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#EnemyEncounter-敌人编成.xlsx
+++ b/Configs/GameConfig/Datas/fg/#EnemyEncounter-敌人编成.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1221,27 +1221,27 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>rh_listen_node</t>
+          <t>fo_aa_west</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>relay_hall</t>
+          <t>foundry_outpost</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>rh_guard_w</t>
+          <t>fo_aa_west</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>enemy_listen_node</t>
+          <t>enemy_aa_gun</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1253,40 +1253,40 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>10</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>rh_prism</t>
+          <t>fo_aa_east</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>relay_hall</t>
+          <t>foundry_outpost</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>rh_guard_e</t>
+          <t>fo_aa_east</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>enemy_prism</t>
+          <t>enemy_aa_gun</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1301,42 +1301,42 @@
         <v>-1</v>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K19" t="n">
-        <v>20</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>rh_hunter_1</t>
+          <t>fo_loader</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>relay_hall</t>
+          <t>foundry_outpost</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>rh_ambush_w</t>
+          <t>fo_loader</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>enemy_echo_hunter</t>
+          <t>enemy_loader</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>rh_ambush_w</t>
+          <t>fo_loader</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1349,39 +1349,39 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>30</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>rh_hunter_2</t>
+          <t>fo_airburst</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>relay_hall</t>
+          <t>foundry_outpost</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>rh_ambush_e</t>
+          <t>fo_airburst</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>enemy_echo_hunter</t>
+          <t>enemy_airburst</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>counter_antiair</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>rh_ambush_e</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -1391,42 +1391,42 @@
         <v>-1</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K21" t="n">
-        <v>40</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>rh_decoy</t>
+          <t>fo_minelayer</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>relay_hall</t>
+          <t>foundry_outpost</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>rh_decoy</t>
+          <t>fo_minelayer</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>enemy_decoy_relay</t>
+          <t>enemy_minelayer</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>counter_minefield</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>fo_minelayer</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -1436,62 +1436,62 @@
         <v>-1</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K22" t="n">
-        <v>50</v>
+        <v>160</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>rh_listener</t>
+          <t>fo_siege_heavy</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>relay_hall</t>
+          <t>foundry_outpost</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>rh_elite</t>
+          <t>fo_siege_heavy</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>enemy_listener</t>
+          <t>enemy_siege_heavy</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>boss_wave</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>fo_siege_heavy</t>
         </is>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>60</v>
+        <v>170</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>rh_counter_prism</t>
+          <t>rh_listen_node</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1501,17 +1501,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>rh_counter_a</t>
+          <t>rh_guard_w</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>enemy_prism</t>
+          <t>enemy_listen_node</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>counter_deflect</t>
+          <t>base</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1523,20 +1523,20 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>70</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>rh_counter_node</t>
+          <t>rh_prism</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>rh_counter_a</t>
+          <t>rh_guard_e</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>enemy_listen_node</t>
+          <t>enemy_prism</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>counter_listen</t>
+          <t>base</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1571,17 +1571,17 @@
         <v>-1</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K25" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>rh_counter_listener</t>
+          <t>rh_hunter_1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1591,22 +1591,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>rh_counter_b</t>
+          <t>rh_ambush_w</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>enemy_listener</t>
+          <t>enemy_echo_hunter</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>counter_listen</t>
+          <t>base</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>rh_ambush_w</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -1619,14 +1619,14 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>rh_counter_jammer</t>
+          <t>rh_hunter_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1636,22 +1636,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>rh_counter_b</t>
+          <t>rh_ambush_e</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>enemy_jammer</t>
+          <t>enemy_echo_hunter</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>counter_jam</t>
+          <t>base</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>rh_ambush_e</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -1664,14 +1664,14 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>rh_node_1</t>
+          <t>rh_decoy</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1681,17 +1681,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>rh_node_1</t>
+          <t>rh_decoy</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>enemy_mind_relay</t>
+          <t>enemy_decoy_relay</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>boss</t>
+          <t>base</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1709,14 +1709,14 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>110</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>rh_node_2</t>
+          <t>rh_listener</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1726,17 +1726,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>rh_node_2</t>
+          <t>rh_elite</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>enemy_mind_relay</t>
+          <t>enemy_listener</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>boss</t>
+          <t>base</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1754,14 +1754,14 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>rh_node_3</t>
+          <t>rh_counter_prism</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1771,17 +1771,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>rh_node_3</t>
+          <t>rh_counter_a</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>enemy_mind_relay</t>
+          <t>enemy_prism</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>boss</t>
+          <t>counter_deflect</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1796,17 +1796,17 @@
         <v>-1</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K30" t="n">
-        <v>130</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>rh_node_4</t>
+          <t>rh_counter_node</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>rh_node_4</t>
+          <t>rh_counter_a</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>enemy_mind_relay</t>
+          <t>enemy_listen_node</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>boss</t>
+          <t>counter_listen</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1844,14 +1844,14 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>140</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>rh_node_5</t>
+          <t>rh_counter_listener</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1861,17 +1861,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>rh_node_5</t>
+          <t>rh_counter_b</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>enemy_mind_relay</t>
+          <t>enemy_listener</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>boss</t>
+          <t>counter_listen</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1889,14 +1889,14 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>150</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>rh_node_6</t>
+          <t>rh_counter_jammer</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1906,17 +1906,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>rh_node_6</t>
+          <t>rh_counter_b</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>enemy_mind_relay</t>
+          <t>enemy_jammer</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>boss</t>
+          <t>counter_jam</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1934,14 +1934,14 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>rh_mind_core</t>
+          <t>rh_node_1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>rh_core</t>
+          <t>rh_node_1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>enemy_mind_core</t>
+          <t>enemy_mind_relay</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1979,14 +1979,14 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>170</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>rh_wave_hunter_1</t>
+          <t>rh_node_2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1996,22 +1996,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>rh_wave_w</t>
+          <t>rh_node_2</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>enemy_echo_hunter</t>
+          <t>enemy_mind_relay</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>boss_wave</t>
+          <t>boss</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>rh_wave_w</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -2024,14 +2024,14 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>rh_wave_hunter_2</t>
+          <t>rh_node_3</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2041,22 +2041,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>rh_wave_e</t>
+          <t>rh_node_3</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>enemy_echo_hunter</t>
+          <t>enemy_mind_relay</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>boss_wave</t>
+          <t>boss</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>rh_wave_e</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -2069,51 +2069,321 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>190</v>
+        <v>130</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
+          <t>rh_node_4</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>relay_hall</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>rh_node_4</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>enemy_mind_relay</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>boss</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>rh_node_5</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>relay_hall</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>rh_node_5</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>enemy_mind_relay</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>boss</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>rh_node_6</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>relay_hall</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>rh_node_6</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>enemy_mind_relay</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>boss</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>rh_mind_core</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>relay_hall</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>rh_core</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>enemy_mind_core</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>boss</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>rh_wave_hunter_1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>relay_hall</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>rh_wave_w</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>enemy_echo_hunter</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>boss_wave</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>rh_wave_w</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>rh_wave_hunter_2</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>relay_hall</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>rh_wave_e</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>enemy_echo_hunter</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>boss_wave</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>rh_wave_e</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>rh_wave_prism</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>relay_hall</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>rh_core_n</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>enemy_prism</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>boss_wave</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J37" t="n">
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J43" t="n">
         <v>3</v>
       </c>
-      <c r="K37" t="n">
+      <c r="K43" t="n">
         <v>200</v>
       </c>
     </row>
